--- a/myworks.xlsx
+++ b/myworks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cnhet\Documents\GitHub\CN-HET-Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF6E649-759D-4917-B216-4973B4D1EEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8513C603-18E3-435A-9A9A-9EBA981CD0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11332" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="发表论文" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="研究生获得奖励" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">发表论文!$A$2:$A$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">发表论文!$A$2:$A$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="358">
   <si>
     <t>papers</t>
   </si>
@@ -215,9 +215,6 @@
   </si>
   <si>
     <t>经济管理出版社</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>碳管理学</t>
@@ -489,26 +486,6 @@
     <t>中国可再生能源电力发展激励政策建模与应用研究</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>华北电力大学创新人才支持与培育计划</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>博士国家奖学金</t>
   </si>
   <si>
@@ -1592,6 +1569,14 @@
   </si>
   <si>
     <t>采访</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>王歌, 卢子仪, 卢天翼. 高比例绿电算力中心综合能源系统规划模型探究[J/OL]. 克拉玛依学刊, 2026, 16(1): 35-44. DOI:10.13677/j.cnki.cn65-1285/c.2026.01.04.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -2078,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultColWidth="11.17578125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2308,22 +2293,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>285</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A69">
-    <sortCondition descending="1" ref="A2:A69"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A68">
+    <sortCondition descending="1" ref="A2:A68"/>
   </sortState>
   <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
@@ -2370,6 +2360,7 @@
     <hyperlink ref="A45" r:id="rId41" display="He Xiaoyu, Gao Wenqing, Lu Taojie, Ruan Ziwen, Wang Ge, Yang Kexin, Li Yan. Navigating closed-loop recycling technologies for a circular economy of wind turbine blades[J/OL]. Energy &amp; Environmental Sustainability, 2025, 1(4): 100056. DOI:10.1016/j.eesus.2025.100056." xr:uid="{00000000-0004-0000-0000-000028000000}"/>
     <hyperlink ref="A47" r:id="rId42" display="https://doi.org/10.18402/resci.2025.07.11" xr:uid="{B55B0BA0-A642-456E-99E7-50B5C53DA626}"/>
     <hyperlink ref="A48" r:id="rId43" display="https://doi.org/10.13677/j.cnki.cn65-1285/c.2025.02.07" xr:uid="{897BA58E-29A4-4437-AAC1-FF10C1254435}"/>
+    <hyperlink ref="A49" r:id="rId44" display="https://doi.org/10.13677/j.cnki.cn65-1285/c.2026.01.04" xr:uid="{0AEC68B0-724B-4270-AC29-CB0F271A7459}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2385,16 +2376,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.899999999999999">
@@ -2402,10 +2393,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2">
         <v>2021</v>
@@ -2416,10 +2407,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D3" s="2">
         <v>2022</v>
@@ -2430,10 +2421,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2">
         <v>2023</v>
@@ -2444,10 +2435,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="D5" s="2">
         <v>2023</v>
@@ -2458,10 +2449,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D6" s="2">
         <v>2024</v>
@@ -2472,10 +2463,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="D7" s="2">
         <v>2024</v>
@@ -2486,10 +2477,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D8" s="2">
         <v>2024</v>
@@ -2500,10 +2491,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D9" s="2">
         <v>2025</v>
@@ -2516,10 +2507,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="D10" s="2">
         <v>2025</v>
@@ -2532,10 +2523,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D11" s="2">
         <v>2025</v>
@@ -2548,10 +2539,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D12" s="2">
         <v>2025</v>
@@ -2564,10 +2555,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2">
         <v>2025</v>
@@ -2586,16 +2577,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" t="s">
         <v>183</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17.649999999999999">
@@ -2606,10 +2597,10 @@
         <v>2023</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17.649999999999999">
@@ -2620,10 +2611,10 @@
         <v>2023</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17.649999999999999">
@@ -2634,10 +2625,10 @@
         <v>2023</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17.649999999999999">
@@ -2648,10 +2639,10 @@
         <v>2023</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17.649999999999999">
@@ -2662,10 +2653,10 @@
         <v>2024</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -2678,10 +2669,10 @@
         <v>2024</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -2694,10 +2685,10 @@
         <v>2024</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -2710,10 +2701,10 @@
         <v>2024</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2726,10 +2717,10 @@
         <v>2024</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="17.649999999999999">
@@ -2740,10 +2731,10 @@
         <v>2025</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2757,10 +2748,10 @@
         <v>2025</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2774,10 +2765,10 @@
         <v>2025</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2791,10 +2782,10 @@
         <v>2025</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -2808,10 +2799,10 @@
         <v>2025</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -2825,10 +2816,10 @@
         <v>2025</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -2842,10 +2833,10 @@
         <v>2025</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -2859,10 +2850,10 @@
         <v>2025</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -2884,16 +2875,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2901,10 +2892,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D2">
         <v>2023</v>
@@ -2915,10 +2906,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D3">
         <v>2023</v>
@@ -2929,10 +2920,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D4">
         <v>2023</v>
@@ -2943,10 +2934,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D5">
         <v>2023</v>
@@ -2957,10 +2948,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D6">
         <v>2024</v>
@@ -2971,10 +2962,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D7">
         <v>2023</v>
@@ -2985,10 +2976,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D8">
         <v>2024</v>
@@ -2999,10 +2990,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D9">
         <v>2024</v>
@@ -3013,10 +3004,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D10">
         <v>2025</v>
@@ -3027,10 +3018,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D11">
         <v>2025</v>
@@ -3041,10 +3032,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D12">
         <v>2025</v>
@@ -3098,28 +3089,28 @@
       <c r="E2" t="s">
         <v>54</v>
       </c>
-      <c r="F2" t="s">
-        <v>55</v>
+      <c r="F2" s="11" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
         <v>56</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
       </c>
       <c r="D3">
         <v>2023</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3138,51 +3129,51 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="C2" s="8">
         <v>30</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F2" s="8">
         <v>2023</v>
@@ -3197,24 +3188,24 @@
         <v>12</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="C3" s="8">
         <v>6</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F3" s="8">
         <v>2020</v>
@@ -3223,30 +3214,30 @@
         <v>6</v>
       </c>
       <c r="H3" s="8">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="I3" s="8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="C4" s="8">
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" s="8">
         <v>2021</v>
@@ -3261,24 +3252,24 @@
         <v>6</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="C5" s="8">
         <v>8</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" s="8">
         <v>2020</v>
@@ -3293,24 +3284,24 @@
         <v>12</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="C6" s="8">
         <v>5</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6" s="8">
         <v>2016</v>
@@ -3325,22 +3316,22 @@
         <v>9</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" s="8">
         <v>2016</v>
@@ -3355,22 +3346,22 @@
         <v>12</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" s="8">
         <v>2018</v>
@@ -3385,22 +3376,22 @@
         <v>12</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" s="8">
         <v>2020</v>
@@ -3415,22 +3406,22 @@
         <v>12</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" s="8">
         <v>2021</v>
@@ -3445,22 +3436,22 @@
         <v>12</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>94</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" s="8">
         <v>2018</v>
@@ -3475,22 +3466,22 @@
         <v>6</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" s="8">
         <v>2020</v>
@@ -3505,24 +3496,24 @@
         <v>12</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="C13" s="8">
         <v>15</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" s="8">
         <v>2022</v>
@@ -3537,24 +3528,24 @@
         <v>12</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="C14" s="8">
         <v>10</v>
       </c>
       <c r="D14" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="F14" s="8">
         <v>2024</v>
@@ -3569,24 +3560,24 @@
         <v>10</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="C15" s="8">
         <v>28.5</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="F15" s="8">
         <v>2025</v>
@@ -3601,24 +3592,24 @@
         <v>3</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" s="8">
         <v>15</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="F16" s="8">
         <v>2025</v>
@@ -3633,24 +3624,24 @@
         <v>6</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1">
       <c r="A17" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>105</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>106</v>
       </c>
       <c r="C17" s="8">
         <v>5</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="F17" s="8">
         <v>2025</v>
@@ -3665,7 +3656,7 @@
         <v>12</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3676,47 +3667,47 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="11.17578125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>108</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>109</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>110</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>111</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>112</v>
-      </c>
-      <c r="H1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>115</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>116</v>
-      </c>
-      <c r="D2" t="s">
-        <v>117</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3733,16 +3724,16 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
         <v>118</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>119</v>
-      </c>
-      <c r="D3" t="s">
-        <v>120</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -3759,16 +3750,16 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" t="s">
         <v>121</v>
-      </c>
-      <c r="C4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" t="s">
-        <v>122</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3785,16 +3776,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
         <v>123</v>
-      </c>
-      <c r="C5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" t="s">
-        <v>124</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -3811,16 +3802,16 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" t="s">
         <v>125</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
         <v>126</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="s">
-        <v>127</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -3837,13 +3828,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" t="s">
         <v>128</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>129</v>
-      </c>
-      <c r="D7" t="s">
-        <v>130</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -3860,99 +3851,105 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G9">
-        <v>11</v>
-      </c>
-      <c r="H9">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" t="s">
         <v>134</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="G12">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -3960,120 +3957,94 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s">
         <v>138</v>
       </c>
-      <c r="C13" t="s">
-        <v>119</v>
-      </c>
       <c r="D13" t="s">
         <v>139</v>
       </c>
       <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>2021</v>
+      </c>
+      <c r="G13">
         <v>12</v>
       </c>
-      <c r="F13">
-        <v>2022</v>
-      </c>
-      <c r="G13">
-        <v>6</v>
-      </c>
       <c r="H13">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s">
         <v>140</v>
       </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
       <c r="E14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H14">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B15" t="s">
         <v>142</v>
       </c>
+      <c r="C15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>143</v>
+      </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>143</v>
+      <c r="A16" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="B16" t="s">
         <v>144</v>
       </c>
-      <c r="C16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>145</v>
-      </c>
+      <c r="C16" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="11"/>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>2025</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="B17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>2025</v>
-      </c>
-      <c r="G17">
-        <v>7</v>
-      </c>
-      <c r="H17">
         <v>1</v>
       </c>
     </row>
@@ -4093,13 +4064,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D1" t="s">
         <v>48</v>
@@ -4110,10 +4081,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D2">
         <v>2023</v>
@@ -4124,10 +4095,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D3">
         <v>2023</v>
@@ -4138,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D4">
         <v>2018</v>
@@ -4152,10 +4123,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D5">
         <v>2018</v>
@@ -4166,10 +4137,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D6">
         <v>2024</v>
@@ -4180,10 +4151,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D7">
         <v>2024</v>
@@ -4194,10 +4165,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D8">
         <v>2025</v>
@@ -4208,10 +4179,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D9">
         <v>2025</v>
@@ -4234,25 +4205,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>292</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4260,16 +4231,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F2" s="11">
         <v>2025</v>
@@ -4283,14 +4254,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F3" s="11">
         <v>2025</v>
@@ -4304,16 +4275,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F4" s="11">
         <v>2025</v>
@@ -4327,16 +4298,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F5" s="11">
         <v>2016</v>
@@ -4350,16 +4321,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F6" s="11">
         <v>2015</v>
@@ -4373,16 +4344,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>336</v>
-      </c>
       <c r="E7" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F7" s="11">
         <v>2015</v>
@@ -4396,16 +4367,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>307</v>
-      </c>
       <c r="E8" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F8" s="11">
         <v>2015</v>
@@ -4419,16 +4390,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F9" s="11">
         <v>2015</v>
@@ -4442,16 +4413,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>312</v>
-      </c>
       <c r="E10" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F10" s="11">
         <v>2016</v>
@@ -4465,16 +4436,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F11" s="11">
         <v>2017</v>
@@ -4488,16 +4459,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F12" s="11">
         <v>2020</v>
@@ -4511,16 +4482,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F13" s="11">
         <v>2017</v>
@@ -4534,16 +4505,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F14" s="11">
         <v>2023</v>
@@ -4557,16 +4528,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F15" s="11">
         <v>2023</v>
@@ -4580,16 +4551,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F16" s="11">
         <v>2023</v>
@@ -4603,16 +4574,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F17" s="11">
         <v>2023</v>
@@ -4626,16 +4597,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F18" s="11">
         <v>2024</v>
@@ -4649,16 +4620,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F19" s="11">
         <v>2022</v>
@@ -4672,16 +4643,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F20" s="11">
         <v>2024</v>
@@ -4695,16 +4666,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>323</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>325</v>
       </c>
       <c r="F21" s="11">
         <v>2022</v>
@@ -4730,22 +4701,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4753,19 +4724,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D2">
         <v>2021</v>
       </c>
       <c r="E2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4781,28 +4752,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" t="s">
         <v>155</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>156</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>157</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>158</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>160</v>
-      </c>
-      <c r="G1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" t="s">
-        <v>162</v>
       </c>
       <c r="I1" t="s">
         <v>50</v>
@@ -4810,10 +4781,10 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C2">
         <v>40</v>
@@ -4831,15 +4802,15 @@
         <v>61</v>
       </c>
       <c r="H2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -4857,15 +4828,15 @@
         <v>51</v>
       </c>
       <c r="H3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -4883,15 +4854,15 @@
         <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C5">
         <v>32</v>
@@ -4909,15 +4880,15 @@
         <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -4935,15 +4906,15 @@
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -4961,15 +4932,15 @@
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C8">
         <v>24</v>
@@ -4988,18 +4959,18 @@
         <v>506</v>
       </c>
       <c r="H8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.649999999999999">
       <c r="A9" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C9">
         <v>32</v>
@@ -5017,15 +4988,15 @@
         <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16.5">
       <c r="A10" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C10">
         <v>32</v>
@@ -5043,15 +5014,15 @@
         <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="16.5">
       <c r="A11" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C11">
         <v>32</v>
@@ -5069,15 +5040,15 @@
         <v>71</v>
       </c>
       <c r="H11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.649999999999999">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -5095,18 +5066,18 @@
         <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.649999999999999">
       <c r="A13" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -5124,18 +5095,18 @@
         <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.649999999999999">
       <c r="A14" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C14">
         <v>32</v>
@@ -5153,15 +5124,15 @@
         <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5">
       <c r="A15" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C15">
         <v>32</v>
@@ -5179,15 +5150,15 @@
         <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5">
       <c r="A16" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16">
         <v>32</v>
@@ -5205,15 +5176,15 @@
         <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.649999999999999">
       <c r="A17" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -5231,18 +5202,18 @@
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.649999999999999">
       <c r="A18" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C18">
         <v>32</v>
@@ -5260,15 +5231,15 @@
         <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16.5">
       <c r="A19" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C19">
         <v>32</v>
@@ -5286,15 +5257,15 @@
         <v>100</v>
       </c>
       <c r="H19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16.5">
       <c r="A20" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C20">
         <v>32</v>
@@ -5312,15 +5283,15 @@
         <v>36</v>
       </c>
       <c r="H20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.649999999999999">
       <c r="A21" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -5338,18 +5309,18 @@
         <v>242</v>
       </c>
       <c r="H21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16.5">
       <c r="A22" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C22">
         <v>16</v>
@@ -5367,18 +5338,18 @@
         <v>223</v>
       </c>
       <c r="H22" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I22" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.649999999999999">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -5396,18 +5367,18 @@
         <v>41</v>
       </c>
       <c r="H23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.649999999999999">
       <c r="A24" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -5425,10 +5396,10 @@
         <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -5444,16 +5415,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" t="s">
         <v>183</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5464,10 +5435,10 @@
         <v>2020</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5478,10 +5449,10 @@
         <v>2020</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5492,10 +5463,10 @@
         <v>2020</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5506,10 +5477,10 @@
         <v>2020</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5520,10 +5491,10 @@
         <v>2020</v>
       </c>
       <c r="C6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5534,10 +5505,10 @@
         <v>2021</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5548,10 +5519,10 @@
         <v>2021</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5562,10 +5533,10 @@
         <v>2022</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5576,10 +5547,10 @@
         <v>2022</v>
       </c>
       <c r="C10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5590,10 +5561,10 @@
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5604,10 +5575,10 @@
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5618,10 +5589,10 @@
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5632,10 +5603,10 @@
         <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -5646,10 +5617,10 @@
         <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5660,10 +5631,10 @@
         <v>2025</v>
       </c>
       <c r="C16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5674,10 +5645,10 @@
         <v>2025</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D17" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -5688,10 +5659,10 @@
         <v>2026</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -5702,10 +5673,10 @@
         <v>2026</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
